--- a/Deliverables/Interface_Board/BOM/Interface_Board.xlsx
+++ b/Deliverables/Interface_Board/BOM/Interface_Board.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Github\ChrisitanRaun-AnnanasMotor\Design-Files\InterfaceBoard-DesignFiles\Project Outputs for Interface_Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ChrisitanRaun-AnnanasMotor\Deliverables\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F0AC9C3-1252-431D-BF46-42A26FB485C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="14430"/>
+    <workbookView xWindow="10155" yWindow="3090" windowWidth="10335" windowHeight="7830" xr2:uid="{6603C336-6A65-460A-B820-F6BEDA4C1421}"/>
   </bookViews>
   <sheets>
     <sheet name="Interface_Board" sheetId="1" r:id="rId1"/>
@@ -17,17 +18,25 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Interface_Board!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="157">
   <si>
     <t>Comment</t>
   </si>
@@ -47,34 +56,43 @@
     <t>Quantity</t>
   </si>
   <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
     <t>10uF</t>
   </si>
   <si>
-    <t>CAP ALUM 10uF 25V SMD</t>
+    <t>CAP CER 10UF 25V X5R 0603</t>
   </si>
   <si>
     <t>C1</t>
   </si>
   <si>
-    <t>RVT1E100M0405.</t>
-  </si>
-  <si>
-    <t>RVT1E100M0405</t>
+    <t>Cap0603</t>
+  </si>
+  <si>
+    <t>GRM188R61E106MA73J</t>
+  </si>
+  <si>
+    <t>Murata</t>
   </si>
   <si>
     <t>22uF</t>
   </si>
   <si>
-    <t>10V 22uF -55℃~+125℃ 6Ω 100kHz ±10% CASE-A_3216 Tantalum Capacitors ROHS</t>
+    <t>CAP CER 22UF 25V X5R 0805</t>
   </si>
   <si>
     <t>C2</t>
   </si>
   <si>
-    <t>Cap Case-A</t>
-  </si>
-  <si>
-    <t>CA45A-A-10V-22uF-K</t>
+    <t>Cap0805</t>
+  </si>
+  <si>
+    <t>CC0805MKX5R8BB226</t>
+  </si>
+  <si>
+    <t>Yageo</t>
   </si>
   <si>
     <t>0.1uF</t>
@@ -86,9 +104,6 @@
     <t>C34, C35, C37, C40</t>
   </si>
   <si>
-    <t>Cap0603</t>
-  </si>
-  <si>
     <t>CC0603KRX7R0BB104</t>
   </si>
   <si>
@@ -104,6 +119,9 @@
     <t>CGA3E2X7R2A223K080AA</t>
   </si>
   <si>
+    <t>TDK</t>
+  </si>
+  <si>
     <t>2.2uF</t>
   </si>
   <si>
@@ -116,6 +134,9 @@
     <t>UMK107BBJ225MA-T</t>
   </si>
   <si>
+    <t>Taiyo Yuden</t>
+  </si>
+  <si>
     <t>100uF</t>
   </si>
   <si>
@@ -128,6 +149,9 @@
     <t>VKMB1001E101MV</t>
   </si>
   <si>
+    <t>Ymin</t>
+  </si>
+  <si>
     <t>63V 10mm 8mm 100uF ±20% ,8x10mm Aluminum Electrolytic Cap</t>
   </si>
   <si>
@@ -146,9 +170,6 @@
     <t>C45</t>
   </si>
   <si>
-    <t>Cap0805</t>
-  </si>
-  <si>
     <t>GCM21BC72A105KE36L</t>
   </si>
   <si>
@@ -164,6 +185,9 @@
     <t>06035A100JAT2A</t>
   </si>
   <si>
+    <t>Kyocera AVX</t>
+  </si>
+  <si>
     <t>1000pF</t>
   </si>
   <si>
@@ -188,6 +212,9 @@
     <t>D2</t>
   </si>
   <si>
+    <t>NXP Semiconductors</t>
+  </si>
+  <si>
     <t>MSK4010</t>
   </si>
   <si>
@@ -197,6 +224,9 @@
     <t>D3</t>
   </si>
   <si>
+    <t>Tak Cheong</t>
+  </si>
+  <si>
     <t>PHF254SMD-x</t>
   </si>
   <si>
@@ -204,6 +234,9 @@
   </si>
   <si>
     <t>J1</t>
+  </si>
+  <si>
+    <t>RTLECS</t>
   </si>
   <si>
     <t>SK07-111071ENL*</t>
@@ -222,6 +255,9 @@
     <t>SK07-111071ENL</t>
   </si>
   <si>
+    <t>SAK ELECTRONICS CO.,LTD</t>
+  </si>
+  <si>
     <t>1125N1202SNM</t>
   </si>
   <si>
@@ -231,6 +267,18 @@
     <t>J4</t>
   </si>
   <si>
+    <t>2.2uH</t>
+  </si>
+  <si>
+    <t>IND SMD 1.5A 2.2uH ±20% 135mΩ</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>MCS20FC-2R2MMP</t>
+  </si>
+  <si>
     <t>33µH</t>
   </si>
   <si>
@@ -243,16 +291,19 @@
     <t>ETQ-P4M330YFN</t>
   </si>
   <si>
-    <t>MTP125-1104S1</t>
-  </si>
-  <si>
-    <t>2.54mm Straight 1 4 Header TH,P=2.54mm Pin Headers ROHS</t>
+    <t>Panasonic</t>
+  </si>
+  <si>
+    <t>C37208</t>
+  </si>
+  <si>
+    <t>Straight 1 6 2.54mm Black Brass Plugin,P=2.54mm Pin Headers ROHS</t>
   </si>
   <si>
     <t>P1</t>
   </si>
   <si>
-    <t>HDR1X4</t>
+    <t>BOOMELEC</t>
   </si>
   <si>
     <t>826629-2</t>
@@ -267,6 +318,9 @@
     <t>HDR1X2</t>
   </si>
   <si>
+    <t>TE Connectivity</t>
+  </si>
+  <si>
     <t>Test Point</t>
   </si>
   <si>
@@ -288,6 +342,9 @@
     <t>Q1</t>
   </si>
   <si>
+    <t>International Rectifier</t>
+  </si>
+  <si>
     <t>10K</t>
   </si>
   <si>
@@ -303,6 +360,18 @@
     <t>AC0603JR-0710KL</t>
   </si>
   <si>
+    <t>100K</t>
+  </si>
+  <si>
+    <t>RES SMD 100K OHM 5% 1/5W 0603</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>CRGH0603J100K</t>
+  </si>
+  <si>
     <t>180m</t>
   </si>
   <si>
@@ -318,6 +387,9 @@
     <t>RTT25R18JTE</t>
   </si>
   <si>
+    <t>RALEC</t>
+  </si>
+  <si>
     <t>1K</t>
   </si>
   <si>
@@ -342,6 +414,9 @@
     <t>CSRN2512FK75L0</t>
   </si>
   <si>
+    <t>Stackpole Electronics</t>
+  </si>
+  <si>
     <t>9K</t>
   </si>
   <si>
@@ -357,6 +432,9 @@
     <t>0805W8F9001T5E</t>
   </si>
   <si>
+    <t>UNI-ROYAL</t>
+  </si>
+  <si>
     <t>49K9</t>
   </si>
   <si>
@@ -390,15 +468,21 @@
     <t>SB1, SB2, SB3, SB4, SB5</t>
   </si>
   <si>
-    <t>AZ1117CH-3.3TRG1</t>
-  </si>
-  <si>
-    <t>15V 1.3V @ 800mA Fixed 3.3V SOT-223 Linear Voltage Regulators (LDO) ROHS</t>
+    <t>TPS62162DSGR</t>
+  </si>
+  <si>
+    <t>Buck Switching Regulator IC Positive Fixed 3.3V 1 Output 1A 8-WFDFN Exposed Pad</t>
   </si>
   <si>
     <t>U1</t>
   </si>
   <si>
+    <t>8-WSON (2x2)</t>
+  </si>
+  <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
     <t>TMC2202-WA-T</t>
   </si>
   <si>
@@ -411,6 +495,9 @@
     <t>32-QFN (5x5)</t>
   </si>
   <si>
+    <t>Trinamic</t>
+  </si>
+  <si>
     <t>XL4001E1</t>
   </si>
   <si>
@@ -418,12 +505,15 @@
   </si>
   <si>
     <t>U7</t>
+  </si>
+  <si>
+    <t>XLSEMI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -474,18 +564,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,7 +607,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -532,7 +619,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -579,6 +666,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -614,6 +718,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -765,659 +886,792 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29B9059-ECD5-4D4B-B6B3-D516DFDB37F9}">
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="4">
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="G4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="4">
+      <c r="C5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="3" t="s">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="D9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="B13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="B15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" s="4">
+        <v>68</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="G15" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F18" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="3" t="s">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="4">
+      <c r="D17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="4">
+      <c r="G20" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F22" s="4">
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="G23" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="4">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F24" s="4">
+      <c r="G25" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F26" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F25" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="G26" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F26" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F27" s="4">
+      <c r="E29" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F28" s="4">
+      <c r="G29" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F29" s="4">
+      <c r="G30" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F31" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F30" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F31" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F32" s="4">
-        <v>1</v>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.30555555555555558" bottom="0.30555555555555558" header="0" footer="0"/>
-  <pageSetup scale="41" orientation="landscape" blackAndWhite="1" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Deliverables/Interface_Board/BOM/Interface_Board.xlsx
+++ b/Deliverables/Interface_Board/BOM/Interface_Board.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ChrisitanRaun-AnnanasMotor\Deliverables\Interface_Board\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F0AC9C3-1252-431D-BF46-42A26FB485C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88884666-C5B9-487E-A9F7-B7B2A319791B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10155" yWindow="3090" windowWidth="10335" windowHeight="7830" xr2:uid="{6603C336-6A65-460A-B820-F6BEDA4C1421}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{26901BDA-4E5E-42C6-A3D1-2469D603E141}"/>
   </bookViews>
   <sheets>
     <sheet name="Interface_Board" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Interface_Board!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="152">
   <si>
     <t>Comment</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Manufacturer</t>
-  </si>
-  <si>
     <t>10uF</t>
   </si>
   <si>
@@ -74,9 +71,6 @@
     <t>GRM188R61E106MA73J</t>
   </si>
   <si>
-    <t>Murata</t>
-  </si>
-  <si>
     <t>22uF</t>
   </si>
   <si>
@@ -92,9 +86,6 @@
     <t>CC0805MKX5R8BB226</t>
   </si>
   <si>
-    <t>Yageo</t>
-  </si>
-  <si>
     <t>0.1uF</t>
   </si>
   <si>
@@ -119,9 +110,6 @@
     <t>CGA3E2X7R2A223K080AA</t>
   </si>
   <si>
-    <t>TDK</t>
-  </si>
-  <si>
     <t>2.2uF</t>
   </si>
   <si>
@@ -134,9 +122,6 @@
     <t>UMK107BBJ225MA-T</t>
   </si>
   <si>
-    <t>Taiyo Yuden</t>
-  </si>
-  <si>
     <t>100uF</t>
   </si>
   <si>
@@ -149,9 +134,6 @@
     <t>VKMB1001E101MV</t>
   </si>
   <si>
-    <t>Ymin</t>
-  </si>
-  <si>
     <t>63V 10mm 8mm 100uF ±20% ,8x10mm Aluminum Electrolytic Cap</t>
   </si>
   <si>
@@ -185,9 +167,6 @@
     <t>06035A100JAT2A</t>
   </si>
   <si>
-    <t>Kyocera AVX</t>
-  </si>
-  <si>
     <t>1000pF</t>
   </si>
   <si>
@@ -212,9 +191,6 @@
     <t>D2</t>
   </si>
   <si>
-    <t>NXP Semiconductors</t>
-  </si>
-  <si>
     <t>MSK4010</t>
   </si>
   <si>
@@ -224,9 +200,6 @@
     <t>D3</t>
   </si>
   <si>
-    <t>Tak Cheong</t>
-  </si>
-  <si>
     <t>PHF254SMD-x</t>
   </si>
   <si>
@@ -234,9 +207,6 @@
   </si>
   <si>
     <t>J1</t>
-  </si>
-  <si>
-    <t>RTLECS</t>
   </si>
   <si>
     <t>SK07-111071ENL*</t>
@@ -255,9 +225,6 @@
     <t>SK07-111071ENL</t>
   </si>
   <si>
-    <t>SAK ELECTRONICS CO.,LTD</t>
-  </si>
-  <si>
     <t>1125N1202SNM</t>
   </si>
   <si>
@@ -291,9 +258,6 @@
     <t>ETQ-P4M330YFN</t>
   </si>
   <si>
-    <t>Panasonic</t>
-  </si>
-  <si>
     <t>C37208</t>
   </si>
   <si>
@@ -303,9 +267,6 @@
     <t>P1</t>
   </si>
   <si>
-    <t>BOOMELEC</t>
-  </si>
-  <si>
     <t>826629-2</t>
   </si>
   <si>
@@ -318,9 +279,6 @@
     <t>HDR1X2</t>
   </si>
   <si>
-    <t>TE Connectivity</t>
-  </si>
-  <si>
     <t>Test Point</t>
   </si>
   <si>
@@ -342,9 +300,6 @@
     <t>Q1</t>
   </si>
   <si>
-    <t>International Rectifier</t>
-  </si>
-  <si>
     <t>10K</t>
   </si>
   <si>
@@ -387,9 +342,6 @@
     <t>RTT25R18JTE</t>
   </si>
   <si>
-    <t>RALEC</t>
-  </si>
-  <si>
     <t>1K</t>
   </si>
   <si>
@@ -414,9 +366,6 @@
     <t>CSRN2512FK75L0</t>
   </si>
   <si>
-    <t>Stackpole Electronics</t>
-  </si>
-  <si>
     <t>9K</t>
   </si>
   <si>
@@ -432,9 +381,6 @@
     <t>0805W8F9001T5E</t>
   </si>
   <si>
-    <t>UNI-ROYAL</t>
-  </si>
-  <si>
     <t>49K9</t>
   </si>
   <si>
@@ -480,9 +426,6 @@
     <t>8-WSON (2x2)</t>
   </si>
   <si>
-    <t>Texas Instruments</t>
-  </si>
-  <si>
     <t>TMC2202-WA-T</t>
   </si>
   <si>
@@ -495,9 +438,6 @@
     <t>32-QFN (5x5)</t>
   </si>
   <si>
-    <t>Trinamic</t>
-  </si>
-  <si>
     <t>XL4001E1</t>
   </si>
   <si>
@@ -507,14 +447,62 @@
     <t>U7</t>
   </si>
   <si>
-    <t>XLSEMI</t>
+    <t xml:space="preserve">QFN-36 Motor Driver ICs ROHS
+</t>
+  </si>
+  <si>
+    <t>U3*</t>
+  </si>
+  <si>
+    <t>48QFP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMC2130-LA-T
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRINAMIC </t>
+  </si>
+  <si>
+    <t>C915795</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>±0.1% 100mW Thin Film Resistor 75V ±50ppm/℃ -55℃~+155℃ 22kΩ 0603 Chip Resistor - Surface Mount ROHS</t>
+  </si>
+  <si>
+    <t>RT0603BRE0722KL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAGEO </t>
+  </si>
+  <si>
+    <t>C705830</t>
+  </si>
+  <si>
+    <t>±1% 100mW Thick Film Resistors 75V ±200ppm/℃ -55℃~+155℃ 2.2Ω 0603 Chip Resistor - Surface Mount ROHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC0603FR-072R2L
+</t>
+  </si>
+  <si>
+    <t>C112307</t>
+  </si>
+  <si>
+    <t>R#3</t>
+  </si>
+  <si>
+    <t>R#4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -522,8 +510,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -533,6 +529,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -561,10 +569,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -573,8 +582,23 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -886,15 +910,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29B9059-ECD5-4D4B-B6B3-D516DFDB37F9}">
-  <dimension ref="A1:G34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39EF4E3A-3E42-4AFA-9A66-9E48A8194848}">
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="19.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -913,765 +936,751 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F4" s="1">
         <v>4</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
       </c>
-      <c r="G5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F8" s="1">
         <v>2</v>
       </c>
-      <c r="G8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="F10" s="1">
         <v>8</v>
       </c>
-      <c r="G10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="C12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="C13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C14" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="C15" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="F15" s="1">
         <v>2</v>
       </c>
-      <c r="G15" s="2" t="s">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="E18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C19" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C20" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F20" s="1">
         <v>2</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>96</v>
+        <v>81</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="F21" s="1">
         <v>5</v>
       </c>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>100</v>
+        <v>85</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="F22" s="1">
         <v>1</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>104</v>
+        <v>88</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="F23" s="1">
         <v>2</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>109</v>
+        <v>93</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="F24" s="1">
         <v>1</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>113</v>
+        <v>97</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="F25" s="1">
         <v>2</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>119</v>
+        <v>102</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="F26" s="1">
         <v>3</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>123</v>
+        <v>106</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="B29" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>134</v>
+        <v>115</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F29" s="1">
         <v>8</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>138</v>
+        <v>119</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="F30" s="1">
         <v>2</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>142</v>
+        <v>123</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F31" s="1">
         <v>5</v>
       </c>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>136</v>
+      </c>
+      <c r="B41" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" t="s">
+        <v>138</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" t="s">
+        <v>140</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I41">
+        <v>7</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F42" s="8"/>
+    </row>
+    <row r="43" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B43" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" t="s">
         <v>144</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="E43" t="s">
         <v>145</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="F43" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="I43">
+        <v>20</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="B44" t="s">
+        <v>151</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="E44" t="s">
+        <v>145</v>
+      </c>
+      <c r="F44" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>156</v>
+      <c r="I44">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="L41" r:id="rId1" xr:uid="{A4C1956C-E5A9-44F9-AF31-F605F8396FED}"/>
+    <hyperlink ref="L43" r:id="rId2" xr:uid="{037B53E4-9F69-40A0-9CF1-C333645A1CC4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>